--- a/public/dl/ke-4aec.xlsx
+++ b/public/dl/ke-4aec.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculadora PVP" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Calculadora PVP" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt formatCode="#,##0.00 €" numFmtId="164"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -153,56 +153,56 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="2" fontId="9" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="4" fontId="5" numFmtId="9" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="4" fontId="11" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="5" fontId="11" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="1" fillId="6" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="6" fontId="5" numFmtId="9" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="6" fontId="11" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -567,8 +567,8 @@
   <dimension ref="B2:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col customWidth="1" max="1" min="1" width="3"/>
+    <col customWidth="1" max="2" min="2" width="80"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -651,7 +651,7 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -665,13 +665,13 @@
   <dimension ref="B2:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col customWidth="1" max="1" min="1" width="5"/>
+    <col customWidth="1" max="2" min="2" width="25"/>
+    <col customWidth="1" max="3" min="3" width="16"/>
+    <col customWidth="1" max="4" min="4" width="14"/>
+    <col customWidth="1" max="5" min="5" width="16"/>
+    <col customWidth="1" max="6" min="6" width="16"/>
+    <col customWidth="1" max="7" min="7" width="14"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -949,6 +949,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>